--- a/employment_forms/020_fintech_software_engineer_job_application--employment_forms.xlsx
+++ b/employment_forms/020_fintech_software_engineer_job_application--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Phd'}</t>
+          <t>Phd</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'software_engineer',_'value':_'software-engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Software Engineer', 'value': 'software-engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'software_development_team_manager',_'value':_'software-development-team-manager'}</t>
+          <t>software_development_team_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Software Development Team Manager', 'value': 'software-development-team-manager'}</t>
+          <t>Software Development Team Manager</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'data_scientist',_'value':_'data-scientist'}</t>
+          <t>data_scientist</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Data Scientist', 'value': 'data-scientist'}</t>
+          <t>Data Scientist</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-Time', 'value': 'full-time'}</t>
+          <t>Full-Time</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-Time', 'value': 'part-time'}</t>
+          <t>Part-Time</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'remote',_'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Remote', 'value': 'remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress',_'value':_'in-progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress', 'value': 'in-progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
